--- a/data/cox_xlsx/VWS.CO.xlsx
+++ b/data/cox_xlsx/VWS.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="500">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -912,52 +912,55 @@
     <t>Debt To Credit Institutions</t>
   </si>
   <si>
+    <t>Financial debts new</t>
+  </si>
+  <si>
+    <t>Lease liabilities- Current Portion</t>
+  </si>
+  <si>
+    <t>Financial debt - Balancing value</t>
+  </si>
+  <si>
+    <t>Tax payables</t>
+  </si>
+  <si>
+    <t>Other liabilities</t>
+  </si>
+  <si>
+    <t>Derivative financial instruments</t>
+  </si>
+  <si>
+    <t>Other liabilities - Balancing value</t>
+  </si>
+  <si>
+    <t>Other Liabilities - Other Payables</t>
+  </si>
+  <si>
+    <t>Other Liabilities - Staff Cost</t>
+  </si>
+  <si>
+    <t>Other Liabilities Tax Duties</t>
+  </si>
+  <si>
+    <t>Prepayments from customers</t>
+  </si>
+  <si>
+    <t>Contract liabilities</t>
+  </si>
+  <si>
+    <t>Liabilities related to assets held for sale</t>
+  </si>
+  <si>
+    <t>Total current liabilities</t>
+  </si>
+  <si>
+    <t>Deferred Tax</t>
+  </si>
+  <si>
+    <t>Pension obligations</t>
+  </si>
+  <si>
     <t>Financial debts</t>
-  </si>
-  <si>
-    <t>Lease liabilities- Current Portion</t>
-  </si>
-  <si>
-    <t>Financial debt - Balancing value</t>
-  </si>
-  <si>
-    <t>Tax payables</t>
-  </si>
-  <si>
-    <t>Other liabilities</t>
-  </si>
-  <si>
-    <t>Derivative financial instruments</t>
-  </si>
-  <si>
-    <t>Other liabilities - Balancing value</t>
-  </si>
-  <si>
-    <t>Other Liabilities - Other Payables</t>
-  </si>
-  <si>
-    <t>Other Liabilities - Staff Cost</t>
-  </si>
-  <si>
-    <t>Other Liabilities Tax Duties</t>
-  </si>
-  <si>
-    <t>Prepayments from customers</t>
-  </si>
-  <si>
-    <t>Contract liabilities</t>
-  </si>
-  <si>
-    <t>Liabilities related to assets held for sale</t>
-  </si>
-  <si>
-    <t>Total current liabilities</t>
-  </si>
-  <si>
-    <t>Deferred Tax</t>
-  </si>
-  <si>
-    <t>Pension obligations</t>
   </si>
   <si>
     <t>Corporate Bond</t>
@@ -16048,14 +16051,38 @@
       <c r="O92" s="18">
         <v>2150.57</v>
       </c>
-      <c r="P92" s="15"/>
-      <c r="Q92" s="15"/>
-      <c r="R92" s="15"/>
-      <c r="S92" s="15"/>
-      <c r="T92" s="15"/>
-      <c r="U92" s="15"/>
-      <c r="V92" s="15"/>
-      <c r="W92" s="15"/>
+      <c r="P92" s="15">
+        <f t="shared" ref="P92:W92" si="1">P93+P94</f>
+        <v>46.42</v>
+      </c>
+      <c r="Q92" s="15">
+        <f t="shared" si="1"/>
+        <v>31.15</v>
+      </c>
+      <c r="R92" s="15">
+        <f t="shared" si="1"/>
+        <v>99.52</v>
+      </c>
+      <c r="S92" s="15">
+        <f t="shared" si="1"/>
+        <v>1058.19</v>
+      </c>
+      <c r="T92" s="15">
+        <f t="shared" si="1"/>
+        <v>198.22</v>
+      </c>
+      <c r="U92" s="15">
+        <f t="shared" si="1"/>
+        <v>91.3</v>
+      </c>
+      <c r="V92" s="15">
+        <f t="shared" si="1"/>
+        <v>408</v>
+      </c>
+      <c r="W92" s="15">
+        <f t="shared" si="1"/>
+        <v>905.34</v>
+      </c>
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
@@ -16181,7 +16208,7 @@
       <c r="W95" s="15"/>
     </row>
     <row r="96" ht="15.0" customHeight="1">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="22" t="s">
         <v>297</v>
       </c>
       <c r="B96" s="18">
@@ -17149,7 +17176,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -17196,7 +17223,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -17229,7 +17256,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -17262,7 +17289,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -17301,7 +17328,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B119" s="15">
         <v>30621.91</v>
@@ -17342,7 +17369,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B120" s="18">
         <v>1618.52</v>
@@ -17381,7 +17408,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B121" s="15">
         <v>29003.39</v>
@@ -17520,7 +17547,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -17549,7 +17576,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -17578,7 +17605,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B126" s="17">
         <v>59117.29</v>
@@ -17649,7 +17676,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -17680,7 +17707,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B128" s="17">
         <v>258147.87</v>
@@ -17751,7 +17778,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B129" s="18">
         <v>318.98</v>
@@ -17822,7 +17849,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B130" s="15">
         <v>47905.8</v>
@@ -17893,7 +17920,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B131" s="23">
         <v>-2540.01</v>
@@ -17964,7 +17991,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -17997,7 +18024,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B133" s="23">
         <v>-2929.87</v>
@@ -18052,7 +18079,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B134" s="18">
         <v>366.23</v>
@@ -18107,7 +18134,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B135" s="19">
         <v>23.63</v>
@@ -18158,7 +18185,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B136" s="17">
         <v>45684.77</v>
@@ -18272,7 +18299,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B138" s="21">
         <v>165.4</v>
@@ -18315,7 +18342,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B139" s="17">
         <v>45850.16</v>
@@ -18386,7 +18413,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B140" s="17">
         <v>303998.03</v>
@@ -18457,7 +18484,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B141" s="18">
         <v>990.42</v>
@@ -18528,7 +18555,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B142" s="19">
         <v>19.45</v>
@@ -18599,7 +18626,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B143" s="18">
         <v>1009.87</v>
@@ -18670,7 +18697,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="15">
@@ -18733,7 +18760,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B145" s="18">
         <v>8222.55</v>
@@ -18790,7 +18817,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B146" s="18">
         <v>2303.73</v>
@@ -18855,7 +18882,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B147" s="15">
         <v>23722.53</v>
@@ -18920,7 +18947,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="18">
@@ -18967,7 +18994,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -19000,7 +19027,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B150" s="18">
         <v>508.0</v>
@@ -19049,7 +19076,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B151" s="18">
         <v>1157.77</v>
@@ -19098,7 +19125,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B152" s="18">
         <v>614.33</v>
@@ -19147,7 +19174,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B153" s="19">
         <v>1.0</v>
@@ -19218,7 +19245,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B154" s="18">
         <v>990.42</v>
@@ -19289,7 +19316,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B155" s="19">
         <v>19.45</v>
@@ -19360,7 +19387,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B156" s="18">
         <v>1009.87</v>
@@ -20294,7 +20321,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -20680,70 +20707,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -20819,7 +20846,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -20917,7 +20944,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B20" s="18">
         <v>9128.01</v>
@@ -20988,7 +21015,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B21" s="20">
         <v>-81.92</v>
@@ -21025,7 +21052,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B22" s="20">
         <v>-93.62</v>
@@ -21083,7 +21110,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -21112,7 +21139,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="19">
@@ -21143,7 +21170,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -21172,7 +21199,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B27" s="15">
         <v>13493.07</v>
@@ -21241,7 +21268,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B28" s="15">
         <v>12393.02</v>
@@ -21312,7 +21339,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="19">
@@ -21381,7 +21408,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="18">
@@ -21450,7 +21477,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B31" s="23">
         <v>-1743.68</v>
@@ -21521,7 +21548,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="23">
@@ -21560,7 +21587,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="18">
@@ -21599,7 +21626,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B34" s="18">
         <v>3030.97</v>
@@ -21670,7 +21697,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B35" s="18">
         <v>479.81</v>
@@ -21735,7 +21762,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="23">
@@ -21780,7 +21807,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B37" s="23">
         <v>-234.05</v>
@@ -21825,7 +21852,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -21856,7 +21883,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -21913,7 +21940,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B40" s="23">
         <v>-2480.95</v>
@@ -21972,7 +21999,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B41" s="18">
         <v>2282.0</v>
@@ -22031,7 +22058,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -22062,7 +22089,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -22093,7 +22120,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -22140,7 +22167,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B45" s="18">
         <v>1930.92</v>
@@ -22211,7 +22238,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B46" s="23">
         <v>-1369.2</v>
@@ -22282,7 +22309,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B47" s="23">
         <v>-3218.21</v>
@@ -22353,7 +22380,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B48" s="15">
         <v>19964.59</v>
@@ -22408,7 +22435,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B49" s="23">
         <v>-409.59</v>
@@ -22437,7 +22464,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B50" s="18">
         <v>6787.49</v>
@@ -22490,7 +22517,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -22555,7 +22582,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -22620,7 +22647,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -22657,7 +22684,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -22694,7 +22721,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -22759,7 +22786,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -22824,7 +22851,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -22857,7 +22884,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -22912,7 +22939,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -22951,7 +22978,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -22984,7 +23011,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -23019,7 +23046,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B62" s="17">
         <v>26752.08</v>
@@ -23090,7 +23117,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B63" s="23">
         <v>-5348.08</v>
@@ -23161,7 +23188,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B64" s="23">
         <v>-9607.81</v>
@@ -23232,7 +23259,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B65" s="18">
         <v>292.56</v>
@@ -23261,7 +23288,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15">
@@ -23292,7 +23319,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B67" s="19">
         <v>23.41</v>
@@ -23363,7 +23390,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B68" s="18">
         <v>222.35</v>
@@ -23430,7 +23457,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B69" s="20">
         <v>-46.81</v>
@@ -23473,7 +23500,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B70" s="15">
         <v>0.0</v>
@@ -23514,7 +23541,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -23543,7 +23570,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B72" s="15">
         <v>0.0</v>
@@ -23580,7 +23607,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -23609,7 +23636,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B74" s="23">
         <v>-222.35</v>
@@ -23668,7 +23695,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="23">
@@ -23709,7 +23736,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B76" s="18">
         <v>1064.93</v>
@@ -23746,7 +23773,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -23777,7 +23804,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -23828,7 +23855,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B79" s="15">
         <v>0.0</v>
@@ -23861,7 +23888,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -23892,7 +23919,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -23925,7 +23952,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -23956,7 +23983,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15">
@@ -23987,7 +24014,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="16" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B84" s="24">
         <v>-13621.79</v>
@@ -24058,7 +24085,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B85" s="23">
         <v>-3300.13</v>
@@ -24125,7 +24152,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B86" s="23">
         <v>-865.99</v>
@@ -24172,7 +24199,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B87" s="23">
         <v>-2527.76</v>
@@ -24213,7 +24240,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B88" s="18">
         <v>1755.39</v>
@@ -24276,7 +24303,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B89" s="23">
         <v>-1427.71</v>
@@ -24317,7 +24344,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -24352,7 +24379,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -24387,7 +24414,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -24426,7 +24453,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -24471,7 +24498,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -24514,7 +24541,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B95" s="25">
         <v>-6366.2</v>
@@ -24585,7 +24612,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B96" s="18">
         <v>6764.09</v>
@@ -24638,7 +24665,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B97" s="15">
         <v>45094.06</v>
@@ -24709,7 +24736,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B98" s="23">
         <v>-128.73</v>
@@ -24780,7 +24807,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B99" s="15">
         <v>51792.61</v>
@@ -24851,7 +24878,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="16" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B100" s="21">
         <v>6635.36</v>
@@ -24922,7 +24949,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B101" s="15">
         <v>13130.29</v>
@@ -25879,7 +25906,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -26055,28 +26082,28 @@
         <v>39</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -26438,7 +26465,7 @@
         <v>45</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z15" s="10" t="s">
         <v>45</v>
@@ -26546,7 +26573,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -26650,33 +26677,33 @@
         <v>70</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="31" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -26711,7 +26738,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="33" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B21" s="34">
         <v>263503.9</v>
@@ -26802,7 +26829,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="33" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B22" s="34">
         <v>278145.56</v>
@@ -26885,7 +26912,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -26920,7 +26947,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B24" s="34">
         <v>277007.31</v>
@@ -27011,7 +27038,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B25" s="34">
         <v>284437.7</v>
@@ -27094,7 +27121,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -27129,7 +27156,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="33" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B27" s="35">
         <v>274.3</v>
@@ -27220,7 +27247,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="33" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B28" s="35">
         <v>281.66</v>
@@ -27303,7 +27330,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="31" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="32"/>
@@ -27338,7 +27365,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="33" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B30" s="37">
         <v>4.35</v>
@@ -27429,7 +27456,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="33" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B31" s="37">
         <v>1.19</v>
@@ -27512,7 +27539,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="32"/>
@@ -27547,7 +27574,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B33" s="37">
         <v>0.32</v>
@@ -27638,7 +27665,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="33" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B34" s="37">
         <v>0.29</v>
@@ -27721,7 +27748,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="33" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B35" s="37">
         <v>0.32</v>
@@ -27812,7 +27839,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="33" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B36" s="37">
         <v>0.29</v>
@@ -27895,7 +27922,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
@@ -27930,7 +27957,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B38" s="36">
         <v>5.95</v>
@@ -28021,7 +28048,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="33" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B39" s="36">
         <v>6.58</v>
@@ -28104,7 +28131,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B40" s="32"/>
       <c r="C40" s="32"/>
@@ -28139,7 +28166,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="33" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B41" s="36">
         <v>53.35</v>
@@ -28226,7 +28253,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="33" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B42" s="36">
         <v>59.71</v>
@@ -28309,7 +28336,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="31" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="32"/>
@@ -28344,7 +28371,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="33" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B44" s="36">
         <v>1.23</v>
@@ -28435,7 +28462,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="33" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B45" s="36">
         <v>1.47</v>
@@ -28518,7 +28545,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="31" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B46" s="32"/>
       <c r="C46" s="32"/>
@@ -28553,7 +28580,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="33" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B47" s="36">
         <v>23.0</v>
@@ -28624,7 +28651,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="33" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B48" s="36">
         <v>83.97</v>
@@ -28683,7 +28710,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="31" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B49" s="32"/>
       <c r="C49" s="32"/>
@@ -28718,7 +28745,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="33" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B50" s="36">
         <v>12.8</v>
@@ -28803,7 +28830,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="33" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B51" s="36">
         <v>27.16</v>
@@ -28886,7 +28913,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="31" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B52" s="32"/>
       <c r="C52" s="32"/>
@@ -28921,7 +28948,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="33" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B53" s="36">
         <v>29.8</v>
@@ -29000,7 +29027,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="33" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B54" s="34"/>
       <c r="C54" s="34"/>
@@ -29069,7 +29096,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="31" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B55" s="32"/>
       <c r="C55" s="32"/>
@@ -29104,7 +29131,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="33" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B56" s="36">
         <v>27.44</v>
@@ -29185,7 +29212,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="33" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B57" s="36">
         <v>6.58</v>
@@ -29268,7 +29295,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="31" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="32"/>
@@ -29303,7 +29330,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="33" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B59" s="36">
         <v>0.52</v>
@@ -29382,7 +29409,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="33" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B60" s="34"/>
       <c r="C60" s="34"/>
@@ -29431,7 +29458,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="31" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B61" s="32"/>
       <c r="C61" s="32"/>
@@ -29466,7 +29493,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="33" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B62" s="36">
         <v>1.19</v>
@@ -29557,7 +29584,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="33" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B63" s="36">
         <v>1.44</v>
@@ -29640,7 +29667,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="31" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="32"/>
@@ -29675,7 +29702,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="33" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B65" s="36">
         <v>10.63</v>
@@ -29762,7 +29789,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="33" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B66" s="36">
         <v>20.27</v>
@@ -29845,7 +29872,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="31" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B67" s="32"/>
       <c r="C67" s="32"/>
@@ -29880,7 +29907,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B68" s="36">
         <v>9.76</v>
@@ -29957,7 +29984,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="33" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B69" s="36">
         <v>18.38</v>
@@ -30036,7 +30063,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B70" s="32"/>
       <c r="C70" s="32"/>
@@ -30071,7 +30098,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="33" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B71" s="36">
         <v>22.13</v>
@@ -30142,7 +30169,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="33" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B72" s="36">
         <v>82.55</v>
